--- a/ProductionBuild/health.result.xlsx
+++ b/ProductionBuild/health.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,163 +367,363 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>avgdividend</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>totaldividends</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>price_end</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>change</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturn</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturnover10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>shares500</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>totalspend</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyearequityproj</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyeardivproj</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>totalfiveyearview</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb Co</t>
+          <t>GSK plc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BMY</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1.809090909090909</v>
+          <t>GSK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
       </c>
       <c r="D2">
-        <v>19.9</v>
+        <v>1.712636363636364</v>
       </c>
       <c r="E2">
-        <v>58.43999862670898</v>
+        <v>18.839</v>
       </c>
       <c r="F2">
-        <v>58.79999923706055</v>
+        <v>38.5099983215332</v>
       </c>
       <c r="G2">
-        <v>0.3600006103515625</v>
+        <v>55.63000106811523</v>
+      </c>
+      <c r="H2">
+        <v>17.12000274658203</v>
+      </c>
+      <c r="I2">
+        <v>35.95900274658203</v>
+      </c>
+      <c r="J2">
+        <v>3.595900274658203</v>
+      </c>
+      <c r="K2">
+        <v>9</v>
+      </c>
+      <c r="L2">
+        <v>500.6700096130371</v>
+      </c>
+      <c r="M2">
+        <v>17.97950137329101</v>
+      </c>
+      <c r="N2">
+        <v>8.563181818181819</v>
+      </c>
+      <c r="O2">
+        <v>26.54268319147283</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Coloplast A/S</t>
+          <t>Roche Holding AG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CLPBY</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0.2578571428571428</v>
+          <t>RHHBY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
       </c>
       <c r="D3">
-        <v>1.805</v>
+        <v>1.2555</v>
       </c>
       <c r="E3">
-        <v>6.730000019073486</v>
+        <v>12.555</v>
       </c>
       <c r="F3">
-        <v>6.559999942779541</v>
+        <v>28.53000068664551</v>
       </c>
       <c r="G3">
-        <v>-0.1700000762939453</v>
+        <v>51.86000061035156</v>
+      </c>
+      <c r="H3">
+        <v>23.32999992370605</v>
+      </c>
+      <c r="I3">
+        <v>35.88499992370605</v>
+      </c>
+      <c r="J3">
+        <v>3.588499992370605</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3">
+        <v>518.6000061035156</v>
+      </c>
+      <c r="M3">
+        <v>17.94249996185303</v>
+      </c>
+      <c r="N3">
+        <v>6.2775</v>
+      </c>
+      <c r="O3">
+        <v>24.21999996185303</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Novo Nordisk A/S</t>
+          <t>Medtronic PLC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVO</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.8756818181818182</v>
+          <t>MDT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
       </c>
       <c r="D4">
-        <v>9.6325</v>
+        <v>2.107272727272727</v>
       </c>
       <c r="E4">
-        <v>17.93000030517578</v>
+        <v>23.18</v>
       </c>
       <c r="F4">
-        <v>39.15000152587891</v>
+        <v>71.23000335693359</v>
       </c>
       <c r="G4">
-        <v>21.22000122070313</v>
+        <v>83.79000091552734</v>
+      </c>
+      <c r="H4">
+        <v>12.55999755859375</v>
+      </c>
+      <c r="I4">
+        <v>35.73999755859375</v>
+      </c>
+      <c r="J4">
+        <v>3.573999755859375</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
+      <c r="L4">
+        <v>502.7400054931641</v>
+      </c>
+      <c r="M4">
+        <v>17.86999877929687</v>
+      </c>
+      <c r="N4">
+        <v>10.53636363636364</v>
+      </c>
+      <c r="O4">
+        <v>28.40636241566051</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Pfizer Inc</t>
+          <t>Novo Nordisk A/S</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1.345180181818182</v>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
       </c>
       <c r="D5">
-        <v>14.796982</v>
+        <v>0.8756818181818182</v>
       </c>
       <c r="E5">
-        <v>30.81593894958496</v>
+        <v>9.6325</v>
       </c>
       <c r="F5">
-        <v>26.79999923706055</v>
+        <v>17.93000030517578</v>
       </c>
       <c r="G5">
-        <v>-4.015939712524414</v>
+        <v>38.52000045776367</v>
+      </c>
+      <c r="H5">
+        <v>20.59000015258789</v>
+      </c>
+      <c r="I5">
+        <v>30.22250015258789</v>
+      </c>
+      <c r="J5">
+        <v>3.022250015258789</v>
+      </c>
+      <c r="K5">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>500.7600059509277</v>
+      </c>
+      <c r="M5">
+        <v>15.11125007629395</v>
+      </c>
+      <c r="N5">
+        <v>4.378409090909091</v>
+      </c>
+      <c r="O5">
+        <v>19.48965916720304</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sonic Healthcare Ltd</t>
+          <t>Sonova Holding AG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SKHHY</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.5212727272727272</v>
+          <t>SONVY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
       </c>
       <c r="D6">
-        <v>5.734</v>
+        <v>0.7465555555555555</v>
       </c>
       <c r="E6">
-        <v>15.35999965667725</v>
+        <v>6.719</v>
       </c>
       <c r="F6">
-        <v>14.3100004196167</v>
+        <v>24.11000061035156</v>
       </c>
       <c r="G6">
-        <v>-1.049999237060547</v>
+        <v>44.29000091552734</v>
+      </c>
+      <c r="H6">
+        <v>20.18000030517578</v>
+      </c>
+      <c r="I6">
+        <v>26.89900030517578</v>
+      </c>
+      <c r="J6">
+        <v>2.689900030517578</v>
+      </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
+      <c r="L6">
+        <v>531.4800109863281</v>
+      </c>
+      <c r="M6">
+        <v>13.44950015258789</v>
+      </c>
+      <c r="N6">
+        <v>3.732777777777778</v>
+      </c>
+      <c r="O6">
+        <v>17.18227793036567</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -537,20 +737,863 @@
           <t>SNY</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D7">
         <v>1.8662</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>18.662</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>40.43999862670898</v>
       </c>
-      <c r="F7">
-        <v>46.90000152587891</v>
-      </c>
       <c r="G7">
-        <v>6.460002899169922</v>
+        <v>47.52999877929688</v>
+      </c>
+      <c r="H7">
+        <v>7.090000152587891</v>
+      </c>
+      <c r="I7">
+        <v>25.75200015258789</v>
+      </c>
+      <c r="J7">
+        <v>2.575200015258789</v>
+      </c>
+      <c r="K7">
+        <v>11</v>
+      </c>
+      <c r="L7">
+        <v>522.8299865722656</v>
+      </c>
+      <c r="M7">
+        <v>12.87600007629394</v>
+      </c>
+      <c r="N7">
+        <v>9.331</v>
+      </c>
+      <c r="O7">
+        <v>22.20700007629394</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chugai Pharmaceutical Co Ltd</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CHGCY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.307</v>
+      </c>
+      <c r="E8">
+        <v>0.614</v>
+      </c>
+      <c r="F8">
+        <v>4.936666965484619</v>
+      </c>
+      <c r="G8">
+        <v>27.8799991607666</v>
+      </c>
+      <c r="H8">
+        <v>22.94333219528198</v>
+      </c>
+      <c r="I8">
+        <v>23.55733219528198</v>
+      </c>
+      <c r="J8">
+        <v>2.355733219528198</v>
+      </c>
+      <c r="K8">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>501.8399848937988</v>
+      </c>
+      <c r="M8">
+        <v>11.77866609764099</v>
+      </c>
+      <c r="N8">
+        <v>1.535</v>
+      </c>
+      <c r="O8">
+        <v>13.31366609764099</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CVS Health Corp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CVS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>2.010909090909091</v>
+      </c>
+      <c r="E9">
+        <v>22.12</v>
+      </c>
+      <c r="F9">
+        <v>78.91000366210938</v>
+      </c>
+      <c r="G9">
+        <v>78.86000061035156</v>
+      </c>
+      <c r="H9">
+        <v>-0.0500030517578125</v>
+      </c>
+      <c r="I9">
+        <v>22.06999694824219</v>
+      </c>
+      <c r="J9">
+        <v>2.206999694824219</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
+      </c>
+      <c r="L9">
+        <v>552.0200042724609</v>
+      </c>
+      <c r="M9">
+        <v>11.03499847412109</v>
+      </c>
+      <c r="N9">
+        <v>10.05454545454545</v>
+      </c>
+      <c r="O9">
+        <v>21.08954392866655</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bristol-Myers Squibb Co</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BMY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>1.809090909090909</v>
+      </c>
+      <c r="E10">
+        <v>19.9</v>
+      </c>
+      <c r="F10">
+        <v>58.43999862670898</v>
+      </c>
+      <c r="G10">
+        <v>59.02000045776367</v>
+      </c>
+      <c r="H10">
+        <v>0.5800018310546875</v>
+      </c>
+      <c r="I10">
+        <v>20.48000183105469</v>
+      </c>
+      <c r="J10">
+        <v>2.048000183105469</v>
+      </c>
+      <c r="K10">
+        <v>9</v>
+      </c>
+      <c r="L10">
+        <v>531.180004119873</v>
+      </c>
+      <c r="M10">
+        <v>10.24000091552734</v>
+      </c>
+      <c r="N10">
+        <v>9.045454545454545</v>
+      </c>
+      <c r="O10">
+        <v>19.28545546098189</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Daiichi Sankyo Company Ltd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DSNKY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.202</v>
+      </c>
+      <c r="E11">
+        <v>0.404</v>
+      </c>
+      <c r="F11">
+        <v>6.766666889190674</v>
+      </c>
+      <c r="G11">
+        <v>17.43000030517578</v>
+      </c>
+      <c r="H11">
+        <v>10.66333341598511</v>
+      </c>
+      <c r="I11">
+        <v>11.06733341598511</v>
+      </c>
+      <c r="J11">
+        <v>1.106733341598511</v>
+      </c>
+      <c r="K11">
+        <v>29</v>
+      </c>
+      <c r="L11">
+        <v>505.4700088500977</v>
+      </c>
+      <c r="M11">
+        <v>5.533666707992554</v>
+      </c>
+      <c r="N11">
+        <v>1.01</v>
+      </c>
+      <c r="O11">
+        <v>6.543666707992553</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Getinge AB publ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GNGBY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.6465</v>
+      </c>
+      <c r="E12">
+        <v>6.465</v>
+      </c>
+      <c r="F12">
+        <v>16.10000038146973</v>
+      </c>
+      <c r="G12">
+        <v>20.44000053405762</v>
+      </c>
+      <c r="H12">
+        <v>4.340000152587891</v>
+      </c>
+      <c r="I12">
+        <v>10.80500015258789</v>
+      </c>
+      <c r="J12">
+        <v>1.080500015258789</v>
+      </c>
+      <c r="K12">
+        <v>25</v>
+      </c>
+      <c r="L12">
+        <v>511.0000133514404</v>
+      </c>
+      <c r="M12">
+        <v>5.402500076293945</v>
+      </c>
+      <c r="N12">
+        <v>3.2325</v>
+      </c>
+      <c r="O12">
+        <v>8.635000076293945</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Pfizer Inc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>1.345180181818182</v>
+      </c>
+      <c r="E13">
+        <v>14.796982</v>
+      </c>
+      <c r="F13">
+        <v>30.81593894958496</v>
+      </c>
+      <c r="G13">
+        <v>26.67000007629395</v>
+      </c>
+      <c r="H13">
+        <v>-4.145938873291016</v>
+      </c>
+      <c r="I13">
+        <v>10.65104312670898</v>
+      </c>
+      <c r="J13">
+        <v>1.065104312670898</v>
+      </c>
+      <c r="K13">
+        <v>19</v>
+      </c>
+      <c r="L13">
+        <v>506.730001449585</v>
+      </c>
+      <c r="M13">
+        <v>5.325521563354492</v>
+      </c>
+      <c r="N13">
+        <v>6.725900909090909</v>
+      </c>
+      <c r="O13">
+        <v>12.0514224724454</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CSL Ltd</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CSLLY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.4470454545454545</v>
+      </c>
+      <c r="E14">
+        <v>4.9175</v>
+      </c>
+      <c r="F14">
+        <v>18.13500022888184</v>
+      </c>
+      <c r="G14">
+        <v>22.85000038146973</v>
+      </c>
+      <c r="H14">
+        <v>4.715000152587891</v>
+      </c>
+      <c r="I14">
+        <v>9.632500152587891</v>
+      </c>
+      <c r="J14">
+        <v>0.9632500152587891</v>
+      </c>
+      <c r="K14">
+        <v>22</v>
+      </c>
+      <c r="L14">
+        <v>502.700008392334</v>
+      </c>
+      <c r="M14">
+        <v>4.816250076293946</v>
+      </c>
+      <c r="N14">
+        <v>2.235227272727273</v>
+      </c>
+      <c r="O14">
+        <v>7.051477349021218</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Smith &amp; Nephew PLC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SNN</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.6652727272727272</v>
+      </c>
+      <c r="E15">
+        <v>7.318</v>
+      </c>
+      <c r="F15">
+        <v>30.07999992370605</v>
+      </c>
+      <c r="G15">
+        <v>31.92000007629395</v>
+      </c>
+      <c r="H15">
+        <v>1.840000152587891</v>
+      </c>
+      <c r="I15">
+        <v>9.15800015258789</v>
+      </c>
+      <c r="J15">
+        <v>0.9158000152587891</v>
+      </c>
+      <c r="K15">
+        <v>16</v>
+      </c>
+      <c r="L15">
+        <v>510.7200012207031</v>
+      </c>
+      <c r="M15">
+        <v>4.579000076293945</v>
+      </c>
+      <c r="N15">
+        <v>3.326363636363636</v>
+      </c>
+      <c r="O15">
+        <v>7.905363712657581</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sonic Healthcare Ltd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SKHHY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.5212727272727272</v>
+      </c>
+      <c r="E16">
+        <v>5.734</v>
+      </c>
+      <c r="F16">
+        <v>15.35999965667725</v>
+      </c>
+      <c r="G16">
+        <v>14.27000045776367</v>
+      </c>
+      <c r="H16">
+        <v>-1.089999198913574</v>
+      </c>
+      <c r="I16">
+        <v>4.644000801086426</v>
+      </c>
+      <c r="J16">
+        <v>0.4644000801086426</v>
+      </c>
+      <c r="K16">
+        <v>36</v>
+      </c>
+      <c r="L16">
+        <v>513.7200164794922</v>
+      </c>
+      <c r="M16">
+        <v>2.322000400543213</v>
+      </c>
+      <c r="N16">
+        <v>2.606363636363636</v>
+      </c>
+      <c r="O16">
+        <v>4.928364036906849</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Medipal Holdings Corp</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MAHLY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.2115</v>
+      </c>
+      <c r="E17">
+        <v>0.423</v>
+      </c>
+      <c r="F17">
+        <v>15.40999984741211</v>
+      </c>
+      <c r="G17">
+        <v>19.10000038146973</v>
+      </c>
+      <c r="H17">
+        <v>3.690000534057617</v>
+      </c>
+      <c r="I17">
+        <v>4.113000534057617</v>
+      </c>
+      <c r="J17">
+        <v>0.4113000534057617</v>
+      </c>
+      <c r="K17">
+        <v>27</v>
+      </c>
+      <c r="L17">
+        <v>515.7000102996826</v>
+      </c>
+      <c r="M17">
+        <v>2.056500267028809</v>
+      </c>
+      <c r="N17">
+        <v>1.0575</v>
+      </c>
+      <c r="O17">
+        <v>3.114000267028809</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Koninklijke Philips NV</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PHG</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.9517142857142857</v>
+      </c>
+      <c r="E18">
+        <v>6.662</v>
+      </c>
+      <c r="F18">
+        <v>30.56999969482422</v>
+      </c>
+      <c r="G18">
+        <v>27.6299991607666</v>
+      </c>
+      <c r="H18">
+        <v>-2.940000534057617</v>
+      </c>
+      <c r="I18">
+        <v>3.721999465942383</v>
+      </c>
+      <c r="J18">
+        <v>0.3721999465942383</v>
+      </c>
+      <c r="K18">
+        <v>19</v>
+      </c>
+      <c r="L18">
+        <v>524.9699840545654</v>
+      </c>
+      <c r="M18">
+        <v>1.860999732971191</v>
+      </c>
+      <c r="N18">
+        <v>4.758571428571429</v>
+      </c>
+      <c r="O18">
+        <v>6.61957116154262</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Astellas Pharma Inc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ALPMY</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.252</v>
+      </c>
+      <c r="E19">
+        <v>0.504</v>
+      </c>
+      <c r="F19">
+        <v>13.85999965667725</v>
+      </c>
+      <c r="G19">
+        <v>15.47999954223633</v>
+      </c>
+      <c r="H19">
+        <v>1.619999885559082</v>
+      </c>
+      <c r="I19">
+        <v>2.123999885559082</v>
+      </c>
+      <c r="J19">
+        <v>0.2123999885559082</v>
+      </c>
+      <c r="K19">
+        <v>33</v>
+      </c>
+      <c r="L19">
+        <v>510.8399848937988</v>
+      </c>
+      <c r="M19">
+        <v>1.061999942779541</v>
+      </c>
+      <c r="N19">
+        <v>1.26</v>
+      </c>
+      <c r="O19">
+        <v>2.321999942779541</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coloplast A/S</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CLPBY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.2578571428571428</v>
+      </c>
+      <c r="E20">
+        <v>1.805</v>
+      </c>
+      <c r="F20">
+        <v>6.730000019073486</v>
+      </c>
+      <c r="G20">
+        <v>6.460000038146973</v>
+      </c>
+      <c r="H20">
+        <v>-0.2699999809265137</v>
+      </c>
+      <c r="I20">
+        <v>1.535000019073486</v>
+      </c>
+      <c r="J20">
+        <v>0.1535000019073486</v>
+      </c>
+      <c r="K20">
+        <v>78</v>
+      </c>
+      <c r="L20">
+        <v>503.8800029754639</v>
+      </c>
+      <c r="M20">
+        <v>0.7675000095367432</v>
+      </c>
+      <c r="N20">
+        <v>1.289285714285714</v>
+      </c>
+      <c r="O20">
+        <v>2.056785723822458</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Cochlear Ltd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CHEOY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.9723000000000001</v>
+      </c>
+      <c r="E21">
+        <v>9.723000000000001</v>
+      </c>
+      <c r="F21">
+        <v>44.29000091552734</v>
+      </c>
+      <c r="G21">
+        <v>33.84000015258789</v>
+      </c>
+      <c r="H21">
+        <v>-10.45000076293945</v>
+      </c>
+      <c r="I21">
+        <v>-0.7270007629394524</v>
+      </c>
+      <c r="J21">
+        <v>-0.07270007629394523</v>
+      </c>
+      <c r="K21">
+        <v>15</v>
+      </c>
+      <c r="L21">
+        <v>507.6000022888184</v>
+      </c>
+      <c r="M21">
+        <v>-0.3635003814697262</v>
+      </c>
+      <c r="N21">
+        <v>4.8615</v>
+      </c>
+      <c r="O21">
+        <v>4.497999618530274</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
   </sheetData>
